--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99263</v>
+        <v>99264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99368</v>
+        <v>99373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108446</v>
+        <v>108448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99381</v>
+        <v>99383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99384</v>
+        <v>99390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99390</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99398</v>
+        <v>99411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 9388-2025 artfynd.xlsx
+++ b/artfynd/A 9388-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136528629</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136539498</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548909</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136541416</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136537357</v>
       </c>
       <c r="B6" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136540245</v>
       </c>
       <c r="B7" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136540207</v>
       </c>
       <c r="B8" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
